--- a/src/transactions_excel.xlsx
+++ b/src/transactions_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/batrerdnneev/my_prj/pythonProject2/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5DBF921-DB71-A141-9F46-F29D5784255B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69321229-B9C6-1D47-B5C2-DACF161F3A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="15960" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="15960" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист 1" sheetId="1" r:id="rId1"/>
